--- a/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
+++ b/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Pablo V\OneDrive - Universidad San Francisco de Quito\USFQ 2021\Investigaciones\Pastas_Mortero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariajosetorresconstante/Documents/GitHub/SingleSolitaryWaveAnalysis/Pastas_Mortero_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF44E96-3F56-4EB1-8F46-930AE9D6793D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470C9D44-A29C-E14F-9861-CE05E80F4118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
   </bookViews>
   <sheets>
     <sheet name="CPT" sheetId="1" r:id="rId1"/>
+    <sheet name="Penetración vs TOF" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,10 +26,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
   <si>
     <t>Tiempo</t>
   </si>
@@ -320,6 +321,15 @@
   <si>
     <t>REF 0.40</t>
   </si>
+  <si>
+    <t>Penetración (mm)</t>
+  </si>
+  <si>
+    <t>TOF (s)</t>
+  </si>
+  <si>
+    <t>0,5,10</t>
+  </si>
 </sst>
 </file>
 
@@ -328,7 +338,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,6 +416,20 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -898,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -962,28 +986,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
@@ -997,9 +1010,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1039,6 +1050,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1059,7 +1096,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1729,6 +1766,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1736,7 +1774,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1778,7 +1815,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2456,6 +2493,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2463,7 +2501,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2492,6 +2529,2495 @@
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16904730308291671"/>
+          <c:y val="6.4646655356972629E-2"/>
+          <c:w val="0.60452133612866055"/>
+          <c:h val="0.68918656275075452"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Penetración vs TOF'!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Penetración (mm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="002060"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$B$5:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$C$5:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>25.166666666666668</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24.599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.166666666666668</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.633333333333333</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.266666666666666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13.166666666666666</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8999999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-54B2-E24E-852C-D098EE4852C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1963225792"/>
+        <c:axId val="1963063280"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Penetración vs TOF'!$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TOF (s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$B$5:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$D$5:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>3.188538838648558E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8237158649864519E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.832086564190206E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.667462813169002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5825157175414721E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5716648111675511E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5879411707254727E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7266157542214843E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-54B2-E24E-852C-D098EE4852C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="342465232"/>
+        <c:axId val="342460800"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1963225792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Tiempo</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1" baseline="0"/>
+                  <a:t> (min)</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-MX" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-EC"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963063280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="25"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1963063280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Penetración (mm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-EC"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963225792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="342460800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="2E-3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>TOF (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-EC"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="342465232"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="342465232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="342460800"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1847717886656233"/>
+          <c:y val="0.57210624078542227"/>
+          <c:w val="0.4124633867653838"/>
+          <c:h val="0.14963595186994036"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-EC"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-EC"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16922153691665509"/>
+          <c:y val="6.4675955868498086E-2"/>
+          <c:w val="0.61194246063362834"/>
+          <c:h val="0.68904568937300437"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Penetración vs TOF'!$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Penetración (mm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$F$5:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$G$5:$G$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.633333333333336</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23.400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15.633333333333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-2D49-6D4D-919B-1A6901702360}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1963225792"/>
+        <c:axId val="1963063280"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Penetración vs TOF'!$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TOF (s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$F$5:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$H$5:$H$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>3.5987030996700309E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.649624853164684E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.9872430544117977E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9193473830871168E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.9475597396674521E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9342286261162384E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.8444761290949239E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.2202777397982718E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.1787730229110855E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000011-2D49-6D4D-919B-1A6901702360}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="580001168"/>
+        <c:axId val="579998576"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1963225792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Tiempo</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1" baseline="0"/>
+                  <a:t> (min)</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-MX" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963063280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="25"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1963063280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Penetración (mm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963225792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="579998576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="4.0000000000000001E-3"/>
+          <c:min val="3.0000000000000001E-3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>TOF (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="580001168"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="580001168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="579998576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15367440530110277"/>
+          <c:y val="0.58867295771896189"/>
+          <c:w val="0.44314564810074536"/>
+          <c:h val="0.16955193034811591"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800"/>
+          </a:pPr>
+          <a:endParaRPr lang="es-EC"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-EC"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Penetración vs TOF'!$K$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Penetración (mm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$J$5:$J$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$K$5:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>32.275000000000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.433333333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5083-4A44-A9E5-D38A52AB0F2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1963225792"/>
+        <c:axId val="1963063280"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Penetración vs TOF'!$L$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TOF (s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$J$5:$J$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>137</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$L$5:$L$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3.541735841195178E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1146636978582523E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.1741886699789687E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.4214730756448883E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.3868044297724392E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.3555538194055997E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0267713562129144E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.8745870000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4375669428413158E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.0005468856826312E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-5083-4A44-A9E5-D38A52AB0F2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="580001168"/>
+        <c:axId val="579998576"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1963225792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Tiempo</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1" baseline="0"/>
+                  <a:t> (min)</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-MX" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963063280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="25"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1963063280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Penetración (mm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963225792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="579998576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>TOF (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="580001168"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="580001168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="579998576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-EC"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16904730308291671"/>
+          <c:y val="6.4646655356972629E-2"/>
+          <c:w val="0.60452133612866055"/>
+          <c:h val="0.68918656275075452"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>TOF 0.3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$B$5:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$D$5:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>3.188538838648558E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8237158649864519E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.832086564190206E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.667462813169002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5825157175414721E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5716648111675511E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5879411707254727E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7266157542214843E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-51B2-2A41-B746-88DA0101C07E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>TOF 0.35</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$F$5:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$H$5:$H$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>3.5987030996700309E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.649624853164684E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.9872430544117977E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9193473830871168E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.9475597396674521E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9342286261162384E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.8444761290949239E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.2202777397982718E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.1787730229110855E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-51B2-2A41-B746-88DA0101C07E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>TOF 0.4</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$J$5:$J$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>137</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Penetración vs TOF'!$L$5:$L$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3.541735841195178E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1146636978582523E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.1741886699789687E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.4214730756448883E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.3868044297724392E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.3555538194055997E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0267713562129144E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.8745870000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4375669428413158E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.0005468856826312E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-51B2-2A41-B746-88DA0101C07E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1963225792"/>
+        <c:axId val="1963063280"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1963225792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Tiempo</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1" baseline="0"/>
+                  <a:t> (min)</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-MX" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963063280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="25"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1963063280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX" b="1"/>
+                  <a:t>Penetración (mm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-EC"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963225792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-EC"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2582,6 +5108,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3099,6 +5705,1038 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3687,6 +7325,161 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>714073</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>122615</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>121394</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>160153</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2816B718-1DDB-AB12-8894-D8997457C017}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>10930</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>102973</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>390267</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>139532</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BAD43BB-0C60-DC49-A160-A313D3B0B24B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>12974</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>161566</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>385653</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1969</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA8F1BCA-27D2-874D-833D-B7266099F66F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>58796</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>94074</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>289265</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>131612</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66422B45-6E67-3F4D-BDC7-20E20456BBE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4013,20 +7806,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08DEF6F-9C93-4516-A42E-FF4987CDC52A}">
   <dimension ref="A1:X17"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="6.796875" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" customWidth="1"/>
-    <col min="9" max="9" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="6.796875" customWidth="1"/>
-    <col min="16" max="16" width="8.796875" customWidth="1"/>
-    <col min="17" max="17" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="6.796875" customWidth="1"/>
-    <col min="24" max="24" width="8.796875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="6.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="6.83203125" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="6.83203125" customWidth="1"/>
+    <col min="24" max="24" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.8" thickBot="1">
+    <row r="1" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="14" t="s">
         <v>9</v>
       </c>
@@ -4066,12 +7859,12 @@
       <c r="N1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="96" t="s">
+      <c r="O1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="97"/>
+      <c r="P1" s="84"/>
     </row>
-    <row r="2" spans="1:24" ht="16.8" thickBot="1">
+    <row r="2" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
@@ -4112,12 +7905,12 @@
       <c r="N2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="98" t="s">
+      <c r="O2" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="99"/>
+      <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="1:24" ht="17.399999999999999" thickBot="1">
+    <row r="3" spans="1:24" ht="19" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
         <v>10</v>
       </c>
@@ -4156,57 +7949,57 @@
       <c r="N3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="100" t="s">
+      <c r="O3" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="101"/>
+      <c r="P3" s="88"/>
     </row>
-    <row r="4" spans="1:24" ht="14.4" thickBot="1">
+    <row r="4" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="5"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:24" ht="14.4" thickBot="1">
-      <c r="A5" s="69">
+    <row r="5" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="60">
         <v>45853</v>
       </c>
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="70">
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="61">
         <v>45853</v>
       </c>
-      <c r="J5" s="91" t="s">
+      <c r="J5" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="73">
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="62">
         <v>45853</v>
       </c>
-      <c r="R5" s="93" t="s">
+      <c r="R5" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="S5" s="94"/>
-      <c r="T5" s="94"/>
-      <c r="U5" s="94"/>
-      <c r="V5" s="94"/>
-      <c r="W5" s="94"/>
-      <c r="X5" s="95"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="82"/>
     </row>
-    <row r="6" spans="1:24" ht="16.8" thickBot="1">
+    <row r="6" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
         <v>0</v>
       </c>
@@ -4280,7 +8073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.4" thickBot="1">
+    <row r="7" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
         <v>1</v>
       </c>
@@ -4308,19 +8101,19 @@
       <c r="I7" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="59" t="s">
+      <c r="K7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="59" t="s">
+      <c r="L7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="59" t="s">
+      <c r="M7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="N7" s="60" t="s">
+      <c r="N7" s="30" t="s">
         <v>2</v>
       </c>
       <c r="O7" s="31" t="s">
@@ -4329,47 +8122,47 @@
       <c r="P7" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="Q7" s="74" t="s">
+      <c r="Q7" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="R7" s="75" t="s">
+      <c r="R7" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="S7" s="76" t="s">
+      <c r="S7" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="T7" s="76" t="s">
+      <c r="T7" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="76" t="s">
+      <c r="U7" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="V7" s="77" t="s">
+      <c r="V7" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="W7" s="78" t="s">
+      <c r="W7" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="X7" s="79" t="s">
+      <c r="X7" s="68" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>0</v>
       </c>
-      <c r="B8" s="61">
+      <c r="B8" s="2">
         <v>27</v>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="26">
         <v>23</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="26">
         <v>25.5</v>
       </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="81">
+      <c r="E8" s="26"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="70">
         <f>AVERAGE(B8:F8)</f>
         <v>25.166666666666668</v>
       </c>
@@ -4380,16 +8173,16 @@
       <c r="I8" s="57">
         <v>0</v>
       </c>
-      <c r="J8" s="61">
+      <c r="J8" s="2">
         <v>39.700000000000003</v>
       </c>
-      <c r="K8" s="62">
+      <c r="K8" s="26">
         <v>39.700000000000003</v>
       </c>
-      <c r="L8" s="62"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="84">
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="73">
         <f>AVERAGE(J8:N8)</f>
         <v>39.700000000000003</v>
       </c>
@@ -4397,17 +8190,17 @@
         <f>$H$3/O8^2</f>
         <v>0.56554645738430853</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="69">
         <v>0</v>
       </c>
-      <c r="R8" s="61">
+      <c r="R8" s="2">
         <v>39.5</v>
       </c>
-      <c r="S8" s="62"/>
-      <c r="T8" s="62"/>
-      <c r="U8" s="62"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="84">
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="73">
         <f>AVERAGE(R8:V8)</f>
         <v>39.5</v>
       </c>
@@ -4416,22 +8209,21 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="64">
+      <c r="B9" s="1">
         <v>22.4</v>
       </c>
-      <c r="C9" s="71">
+      <c r="C9">
         <v>25.4</v>
       </c>
-      <c r="D9" s="71">
+      <c r="D9">
         <v>26</v>
       </c>
-      <c r="E9" s="71"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="82">
+      <c r="F9" s="59"/>
+      <c r="G9" s="71">
         <f t="shared" ref="G9:G16" si="1">AVERAGE(B9:F9)</f>
         <v>24.599999999999998</v>
       </c>
@@ -4442,14 +8234,11 @@
       <c r="I9" s="57">
         <v>5</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="1">
         <v>39.700000000000003</v>
       </c>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="66"/>
-      <c r="O9" s="85">
+      <c r="N9" s="59"/>
+      <c r="O9" s="74">
         <f t="shared" ref="O9:O17" si="3">AVERAGE(J9:N9)</f>
         <v>39.700000000000003</v>
       </c>
@@ -4460,14 +8249,11 @@
       <c r="Q9" s="57">
         <v>5</v>
       </c>
-      <c r="R9" s="64">
+      <c r="R9" s="1">
         <v>39.5</v>
       </c>
-      <c r="S9" s="65"/>
-      <c r="T9" s="65"/>
-      <c r="U9" s="65"/>
-      <c r="V9" s="66"/>
-      <c r="W9" s="85">
+      <c r="V9" s="59"/>
+      <c r="W9" s="74">
         <f t="shared" ref="W9:W17" si="5">AVERAGE(R9:V9)</f>
         <v>39.5</v>
       </c>
@@ -4476,22 +8262,21 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="B10" s="64">
+      <c r="B10" s="1">
         <v>20</v>
       </c>
-      <c r="C10" s="71">
+      <c r="C10">
         <v>17</v>
       </c>
-      <c r="D10" s="71">
+      <c r="D10">
         <v>23.5</v>
       </c>
-      <c r="E10" s="71"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="82">
+      <c r="F10" s="59"/>
+      <c r="G10" s="71">
         <f>AVERAGE(B10:F10)</f>
         <v>20.166666666666668</v>
       </c>
@@ -4502,14 +8287,11 @@
       <c r="I10" s="57">
         <v>10</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="1">
         <v>39.700000000000003</v>
       </c>
-      <c r="K10" s="65"/>
-      <c r="L10" s="65"/>
-      <c r="M10" s="65"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="85">
+      <c r="N10" s="59"/>
+      <c r="O10" s="74">
         <f t="shared" si="3"/>
         <v>39.700000000000003</v>
       </c>
@@ -4520,14 +8302,11 @@
       <c r="Q10" s="57">
         <v>10</v>
       </c>
-      <c r="R10" s="64">
+      <c r="R10" s="1">
         <v>39.5</v>
       </c>
-      <c r="S10" s="65"/>
-      <c r="T10" s="65"/>
-      <c r="U10" s="65"/>
-      <c r="V10" s="66"/>
-      <c r="W10" s="85">
+      <c r="V10" s="59"/>
+      <c r="W10" s="74">
         <f t="shared" si="5"/>
         <v>39.5</v>
       </c>
@@ -4536,22 +8315,21 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20</v>
       </c>
-      <c r="B11" s="64">
+      <c r="B11" s="1">
         <v>18</v>
       </c>
-      <c r="C11" s="71">
+      <c r="C11">
         <v>21.1</v>
       </c>
-      <c r="D11" s="71">
+      <c r="D11">
         <v>21.5</v>
       </c>
-      <c r="E11" s="71"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="82">
+      <c r="F11" s="59"/>
+      <c r="G11" s="71">
         <f t="shared" si="1"/>
         <v>20.2</v>
       </c>
@@ -4562,14 +8340,11 @@
       <c r="I11" s="57">
         <v>20</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="1">
         <v>39.700000000000003</v>
       </c>
-      <c r="K11" s="65"/>
-      <c r="L11" s="65"/>
-      <c r="M11" s="65"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="85">
+      <c r="N11" s="59"/>
+      <c r="O11" s="74">
         <f t="shared" si="3"/>
         <v>39.700000000000003</v>
       </c>
@@ -4580,14 +8355,11 @@
       <c r="Q11" s="57">
         <v>20</v>
       </c>
-      <c r="R11" s="64">
+      <c r="R11" s="1">
         <v>39.5</v>
       </c>
-      <c r="S11" s="65"/>
-      <c r="T11" s="65"/>
-      <c r="U11" s="65"/>
-      <c r="V11" s="66"/>
-      <c r="W11" s="85">
+      <c r="V11" s="59"/>
+      <c r="W11" s="74">
         <f t="shared" si="5"/>
         <v>39.5</v>
       </c>
@@ -4596,22 +8368,21 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>30</v>
       </c>
-      <c r="B12" s="64">
+      <c r="B12" s="1">
         <v>18.8</v>
       </c>
-      <c r="C12" s="71">
+      <c r="C12">
         <v>17.7</v>
       </c>
-      <c r="D12" s="71">
+      <c r="D12">
         <v>16.399999999999999</v>
       </c>
-      <c r="E12" s="71"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="82">
+      <c r="F12" s="59"/>
+      <c r="G12" s="71">
         <f t="shared" si="1"/>
         <v>17.633333333333333</v>
       </c>
@@ -4622,14 +8393,11 @@
       <c r="I12" s="57">
         <v>30</v>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="1">
         <v>36.5</v>
       </c>
-      <c r="K12" s="65"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="65"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="85">
+      <c r="N12" s="59"/>
+      <c r="O12" s="74">
         <f t="shared" si="3"/>
         <v>36.5</v>
       </c>
@@ -4640,14 +8408,11 @@
       <c r="Q12" s="57">
         <v>30</v>
       </c>
-      <c r="R12" s="64">
+      <c r="R12" s="1">
         <v>39.5</v>
       </c>
-      <c r="S12" s="65"/>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65"/>
-      <c r="V12" s="66"/>
-      <c r="W12" s="85">
+      <c r="V12" s="59"/>
+      <c r="W12" s="74">
         <f t="shared" si="5"/>
         <v>39.5</v>
       </c>
@@ -4656,22 +8421,21 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>40</v>
       </c>
-      <c r="B13" s="64">
+      <c r="B13" s="1">
         <v>13</v>
       </c>
-      <c r="C13" s="71">
+      <c r="C13">
         <v>15.4</v>
       </c>
-      <c r="D13" s="71">
+      <c r="D13">
         <v>17.399999999999999</v>
       </c>
-      <c r="E13" s="71"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="82">
+      <c r="F13" s="59"/>
+      <c r="G13" s="71">
         <f t="shared" si="1"/>
         <v>15.266666666666666</v>
       </c>
@@ -4682,16 +8446,14 @@
       <c r="I13" s="57">
         <v>40</v>
       </c>
-      <c r="J13" s="64">
+      <c r="J13" s="1">
         <v>34.5</v>
       </c>
-      <c r="K13" s="65">
+      <c r="K13">
         <v>35.1</v>
       </c>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="66"/>
-      <c r="O13" s="85">
+      <c r="N13" s="59"/>
+      <c r="O13" s="74">
         <f t="shared" si="3"/>
         <v>34.799999999999997</v>
       </c>
@@ -4702,14 +8464,11 @@
       <c r="Q13" s="57">
         <v>40</v>
       </c>
-      <c r="R13" s="64">
+      <c r="R13" s="1">
         <v>39.5</v>
       </c>
-      <c r="S13" s="65"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65"/>
-      <c r="V13" s="66"/>
-      <c r="W13" s="85">
+      <c r="V13" s="59"/>
+      <c r="W13" s="74">
         <f t="shared" si="5"/>
         <v>39.5</v>
       </c>
@@ -4718,22 +8477,21 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>60</v>
       </c>
-      <c r="B14" s="64">
+      <c r="B14" s="1">
         <v>13.9</v>
       </c>
-      <c r="C14" s="71">
+      <c r="C14">
         <v>12.6</v>
       </c>
-      <c r="D14" s="71">
+      <c r="D14">
         <v>13</v>
       </c>
-      <c r="E14" s="71"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="82">
+      <c r="F14" s="59"/>
+      <c r="G14" s="71">
         <f t="shared" si="1"/>
         <v>13.166666666666666</v>
       </c>
@@ -4744,18 +8502,17 @@
       <c r="I14" s="57">
         <v>60</v>
       </c>
-      <c r="J14" s="64">
+      <c r="J14" s="1">
         <v>29.5</v>
       </c>
-      <c r="K14" s="65">
+      <c r="K14">
         <v>30.7</v>
       </c>
-      <c r="L14" s="65">
+      <c r="L14">
         <v>28.7</v>
       </c>
-      <c r="M14" s="65"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="85">
+      <c r="N14" s="59"/>
+      <c r="O14" s="74">
         <f t="shared" si="3"/>
         <v>29.633333333333336</v>
       </c>
@@ -4766,20 +8523,20 @@
       <c r="Q14" s="57">
         <v>60</v>
       </c>
-      <c r="R14" s="64">
+      <c r="R14" s="1">
         <v>34.5</v>
       </c>
-      <c r="S14" s="65">
+      <c r="S14">
         <v>28</v>
       </c>
-      <c r="T14" s="65">
+      <c r="T14">
         <v>32.4</v>
       </c>
-      <c r="U14" s="65">
+      <c r="U14">
         <v>34.200000000000003</v>
       </c>
-      <c r="V14" s="66"/>
-      <c r="W14" s="85">
+      <c r="V14" s="59"/>
+      <c r="W14" s="74">
         <f t="shared" si="5"/>
         <v>32.275000000000006</v>
       </c>
@@ -4788,22 +8545,21 @@
         <v>0.85569067243829822</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>90</v>
       </c>
-      <c r="B15" s="64">
+      <c r="B15" s="1">
         <v>6.2</v>
       </c>
-      <c r="C15" s="71">
+      <c r="C15">
         <v>5.8</v>
       </c>
-      <c r="D15" s="88">
+      <c r="D15">
         <v>5.7</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="82">
+      <c r="F15" s="59"/>
+      <c r="G15" s="71">
         <f t="shared" si="1"/>
         <v>5.8999999999999995</v>
       </c>
@@ -4814,18 +8570,17 @@
       <c r="I15" s="57">
         <v>90</v>
       </c>
-      <c r="J15" s="64">
+      <c r="J15" s="1">
         <v>22</v>
       </c>
-      <c r="K15" s="65">
+      <c r="K15">
         <v>25.7</v>
       </c>
-      <c r="L15" s="65">
+      <c r="L15">
         <v>22.5</v>
       </c>
-      <c r="M15" s="65"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="85">
+      <c r="N15" s="59"/>
+      <c r="O15" s="74">
         <f t="shared" si="3"/>
         <v>23.400000000000002</v>
       </c>
@@ -4836,18 +8591,17 @@
       <c r="Q15" s="57">
         <v>90</v>
       </c>
-      <c r="R15" s="64">
+      <c r="R15" s="1">
         <v>30.7</v>
       </c>
-      <c r="S15" s="65">
+      <c r="S15">
         <v>29.1</v>
       </c>
-      <c r="T15" s="65">
+      <c r="T15">
         <v>30.5</v>
       </c>
-      <c r="U15" s="65"/>
-      <c r="V15" s="66"/>
-      <c r="W15" s="85">
+      <c r="V15" s="59"/>
+      <c r="W15" s="74">
         <f t="shared" si="5"/>
         <v>30.099999999999998</v>
       </c>
@@ -4856,22 +8610,22 @@
         <v>0.98382149867974411</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="14.4" thickBot="1">
+    <row r="16" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>120</v>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="3">
         <v>4</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="27">
         <v>3.3</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="27">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E16" s="59"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="83">
+      <c r="E16" s="27"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="72">
         <f t="shared" si="1"/>
         <v>3.9666666666666663</v>
       </c>
@@ -4882,18 +8636,16 @@
       <c r="I16" s="57">
         <v>120</v>
       </c>
-      <c r="J16" s="64">
+      <c r="J16" s="1">
         <v>16.7</v>
       </c>
-      <c r="K16" s="65">
+      <c r="K16">
         <v>14.8</v>
       </c>
-      <c r="L16" s="65">
+      <c r="L16">
         <v>15.4</v>
       </c>
-      <c r="M16" s="65"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="85">
+      <c r="O16" s="74">
         <f t="shared" si="3"/>
         <v>15.633333333333333</v>
       </c>
@@ -4904,18 +8656,16 @@
       <c r="Q16" s="57">
         <v>120</v>
       </c>
-      <c r="R16" s="64">
+      <c r="R16" s="1">
         <v>23.8</v>
       </c>
-      <c r="S16" s="65">
+      <c r="S16">
         <v>25</v>
       </c>
-      <c r="T16" s="65">
+      <c r="T16">
         <v>24.5</v>
       </c>
-      <c r="U16" s="65"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="85">
+      <c r="W16" s="74">
         <f t="shared" si="5"/>
         <v>24.433333333333334</v>
       </c>
@@ -4924,22 +8674,22 @@
         <v>1.4930826881193389</v>
       </c>
     </row>
-    <row r="17" spans="9:24" ht="14.4" thickBot="1">
+    <row r="17" spans="9:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I17" s="58">
         <v>150</v>
       </c>
-      <c r="J17" s="67">
+      <c r="J17" s="3">
         <v>11.8</v>
       </c>
-      <c r="K17" s="68">
+      <c r="K17" s="27">
         <v>12</v>
       </c>
-      <c r="L17" s="68">
+      <c r="L17" s="27">
         <v>11.6</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="86">
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="75">
         <f t="shared" si="3"/>
         <v>11.799999999999999</v>
       </c>
@@ -4961,7 +8711,7 @@
       </c>
       <c r="U17" s="27"/>
       <c r="V17" s="27"/>
-      <c r="W17" s="87">
+      <c r="W17" s="75">
         <f t="shared" si="5"/>
         <v>15.933333333333332</v>
       </c>
@@ -4983,4 +8733,364 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF7CE1B-CDE6-724F-B93E-F8F0CB386150}">
+  <dimension ref="B3:M30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" s="96">
+        <v>0.3</v>
+      </c>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="96">
+        <v>0.35</v>
+      </c>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="98">
+        <v>0.4</v>
+      </c>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B4" s="89"/>
+      <c r="C4" s="89" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="92" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="89">
+        <v>0</v>
+      </c>
+      <c r="C5" s="90">
+        <v>25.166666666666668</v>
+      </c>
+      <c r="D5" s="89">
+        <v>3.188538838648558E-3</v>
+      </c>
+      <c r="F5" s="89">
+        <v>0</v>
+      </c>
+      <c r="G5" s="91">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="H5" s="89">
+        <v>3.5987030996700309E-3</v>
+      </c>
+      <c r="J5" s="92">
+        <v>0</v>
+      </c>
+      <c r="K5" s="93">
+        <v>39.5</v>
+      </c>
+      <c r="L5" s="92">
+        <v>3.541735841195178E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="89">
+        <v>5</v>
+      </c>
+      <c r="C6" s="90">
+        <v>24.599999999999998</v>
+      </c>
+      <c r="D6" s="89">
+        <v>2.8237158649864519E-3</v>
+      </c>
+      <c r="F6" s="89">
+        <v>5</v>
+      </c>
+      <c r="G6" s="91">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="H6" s="89">
+        <v>3.649624853164684E-3</v>
+      </c>
+      <c r="J6" s="92">
+        <v>5</v>
+      </c>
+      <c r="K6" s="93">
+        <v>39.5</v>
+      </c>
+      <c r="L6" s="92">
+        <v>4.1146636978582523E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B7" s="89">
+        <v>10</v>
+      </c>
+      <c r="C7" s="90">
+        <v>20.166666666666668</v>
+      </c>
+      <c r="D7" s="89">
+        <v>2.832086564190206E-3</v>
+      </c>
+      <c r="F7" s="89">
+        <v>10</v>
+      </c>
+      <c r="G7" s="91">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="H7" s="89">
+        <v>3.9872430544117977E-3</v>
+      </c>
+      <c r="J7" s="92">
+        <v>10</v>
+      </c>
+      <c r="K7" s="93">
+        <v>39.5</v>
+      </c>
+      <c r="L7" s="92">
+        <v>4.1741886699789687E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B8" s="89">
+        <v>20</v>
+      </c>
+      <c r="C8" s="90">
+        <v>20.2</v>
+      </c>
+      <c r="D8" s="89">
+        <v>2.667462813169002E-3</v>
+      </c>
+      <c r="F8" s="89">
+        <v>20</v>
+      </c>
+      <c r="G8" s="91">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="H8" s="89">
+        <v>3.9193473830871168E-3</v>
+      </c>
+      <c r="J8" s="92">
+        <v>20</v>
+      </c>
+      <c r="K8" s="93">
+        <v>39.5</v>
+      </c>
+      <c r="L8" s="92">
+        <v>4.4214730756448883E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="89">
+        <v>30</v>
+      </c>
+      <c r="C9" s="90">
+        <v>17.633333333333333</v>
+      </c>
+      <c r="D9" s="89">
+        <v>2.5825157175414721E-3</v>
+      </c>
+      <c r="F9" s="89">
+        <v>30</v>
+      </c>
+      <c r="G9" s="91">
+        <v>36.5</v>
+      </c>
+      <c r="H9" s="89">
+        <v>3.9475597396674521E-3</v>
+      </c>
+      <c r="J9" s="92">
+        <v>30</v>
+      </c>
+      <c r="K9" s="93">
+        <v>39.5</v>
+      </c>
+      <c r="L9" s="92">
+        <v>4.3868044297724392E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="89">
+        <v>40</v>
+      </c>
+      <c r="C10" s="90">
+        <v>15.266666666666666</v>
+      </c>
+      <c r="D10" s="89">
+        <v>2.5716648111675511E-3</v>
+      </c>
+      <c r="F10" s="89">
+        <v>40</v>
+      </c>
+      <c r="G10" s="91">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="H10" s="89">
+        <v>3.9342286261162384E-3</v>
+      </c>
+      <c r="J10" s="92">
+        <v>40</v>
+      </c>
+      <c r="K10" s="93">
+        <v>39.5</v>
+      </c>
+      <c r="L10" s="94">
+        <v>4.3555538194055997E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="89">
+        <v>60</v>
+      </c>
+      <c r="C11" s="90">
+        <v>13.166666666666666</v>
+      </c>
+      <c r="D11" s="89">
+        <v>2.5879411707254727E-3</v>
+      </c>
+      <c r="F11" s="89">
+        <v>60</v>
+      </c>
+      <c r="G11" s="91">
+        <v>29.633333333333336</v>
+      </c>
+      <c r="H11" s="89">
+        <v>3.8444761290949239E-3</v>
+      </c>
+      <c r="J11" s="92">
+        <v>60</v>
+      </c>
+      <c r="K11" s="93">
+        <v>32.275000000000006</v>
+      </c>
+      <c r="L11" s="92">
+        <v>4.0267713562129144E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="89">
+        <v>90</v>
+      </c>
+      <c r="C12" s="90">
+        <v>5.8999999999999995</v>
+      </c>
+      <c r="D12" s="89">
+        <v>2.7266157542214843E-3</v>
+      </c>
+      <c r="F12" s="89">
+        <v>90</v>
+      </c>
+      <c r="G12" s="91">
+        <v>23.400000000000002</v>
+      </c>
+      <c r="H12" s="89">
+        <v>3.2202777397982718E-3</v>
+      </c>
+      <c r="J12" s="92">
+        <v>90</v>
+      </c>
+      <c r="K12" s="93">
+        <v>30.099999999999998</v>
+      </c>
+      <c r="L12" s="92">
+        <v>3.8745870000000001E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="89">
+        <v>120</v>
+      </c>
+      <c r="C13" s="90">
+        <v>3.9666666666666663</v>
+      </c>
+      <c r="D13" s="89"/>
+      <c r="F13" s="89">
+        <v>120</v>
+      </c>
+      <c r="G13" s="91">
+        <v>15.633333333333333</v>
+      </c>
+      <c r="H13" s="89">
+        <v>3.1787730229110855E-3</v>
+      </c>
+      <c r="J13" s="92">
+        <v>120</v>
+      </c>
+      <c r="K13" s="93">
+        <v>24.433333333333334</v>
+      </c>
+      <c r="L13" s="95">
+        <f>AVERAGE(L12,L14)</f>
+        <v>3.4375669428413158E-3</v>
+      </c>
+      <c r="M13" s="95"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="F14" s="89">
+        <v>150</v>
+      </c>
+      <c r="G14" s="91">
+        <v>11.799999999999999</v>
+      </c>
+      <c r="H14" s="89"/>
+      <c r="J14" s="92">
+        <v>137</v>
+      </c>
+      <c r="L14" s="92">
+        <v>3.0005468856826312E-3</v>
+      </c>
+      <c r="M14" s="95">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="J15" s="92">
+        <v>150</v>
+      </c>
+      <c r="K15" s="93">
+        <v>15.933333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="7:11" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>0.5</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="J3:L3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
+++ b/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariajosetorresconstante/Documents/GitHub/SingleSolitaryWaveAnalysis/Pastas_Mortero_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470C9D44-A29C-E14F-9861-CE05E80F4118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD087DA-5375-5E40-9A82-5DC093B38C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" activeTab="1" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
   </bookViews>
   <sheets>
     <sheet name="CPT" sheetId="1" r:id="rId1"/>
@@ -922,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1011,6 +1011,23 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1050,29 +1067,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2873,7 +2870,7 @@
                   <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-EC"/>
+              <a:endParaRPr lang="es-MX"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3123,6 +3120,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="342460800"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -7859,10 +7857,10 @@
       <c r="N1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="83" t="s">
+      <c r="O1" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="84"/>
+      <c r="P1" s="91"/>
     </row>
     <row r="2" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
@@ -7905,10 +7903,10 @@
       <c r="N2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="85" t="s">
+      <c r="O2" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="86"/>
+      <c r="P2" s="93"/>
     </row>
     <row r="3" spans="1:24" ht="19" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
@@ -7949,10 +7947,10 @@
       <c r="N3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="87" t="s">
+      <c r="O3" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="88"/>
+      <c r="P3" s="95"/>
     </row>
     <row r="4" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
@@ -7965,39 +7963,39 @@
       <c r="A5" s="60">
         <v>45853</v>
       </c>
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
       <c r="I5" s="61">
         <v>45853</v>
       </c>
-      <c r="J5" s="78" t="s">
+      <c r="J5" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="79"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="86"/>
       <c r="Q5" s="62">
         <v>45853</v>
       </c>
-      <c r="R5" s="80" t="s">
+      <c r="R5" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="82"/>
+      <c r="S5" s="88"/>
+      <c r="T5" s="88"/>
+      <c r="U5" s="88"/>
+      <c r="V5" s="88"/>
+      <c r="W5" s="88"/>
+      <c r="X5" s="89"/>
     </row>
     <row r="6" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
@@ -8753,326 +8751,326 @@
       </c>
       <c r="C3" s="96"/>
       <c r="D3" s="96"/>
-      <c r="E3" s="97"/>
+      <c r="E3" s="82"/>
       <c r="F3" s="96">
         <v>0.35</v>
       </c>
       <c r="G3" s="96"/>
       <c r="H3" s="96"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="98">
+      <c r="I3" s="82"/>
+      <c r="J3" s="97">
         <v>0.4</v>
       </c>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="89"/>
-      <c r="C4" s="89" t="s">
+      <c r="B4" s="76"/>
+      <c r="C4" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="89" t="s">
+      <c r="D4" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89" t="s">
+      <c r="F4" s="76"/>
+      <c r="G4" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="89" t="s">
+      <c r="H4" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92" t="s">
+      <c r="J4" s="79"/>
+      <c r="K4" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="92" t="s">
+      <c r="L4" s="79" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="89">
+      <c r="B5" s="76">
         <v>0</v>
       </c>
-      <c r="C5" s="90">
+      <c r="C5" s="77">
         <v>25.166666666666668</v>
       </c>
-      <c r="D5" s="89">
+      <c r="D5" s="76">
         <v>3.188538838648558E-3</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="76">
         <v>0</v>
       </c>
-      <c r="G5" s="91">
+      <c r="G5" s="78">
         <v>39.700000000000003</v>
       </c>
-      <c r="H5" s="89">
+      <c r="H5" s="76">
         <v>3.5987030996700309E-3</v>
       </c>
-      <c r="J5" s="92">
+      <c r="J5" s="79">
         <v>0</v>
       </c>
-      <c r="K5" s="93">
+      <c r="K5" s="80">
         <v>39.5</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="79">
         <v>3.541735841195178E-3</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="89">
+      <c r="B6" s="76">
         <v>5</v>
       </c>
-      <c r="C6" s="90">
+      <c r="C6" s="77">
         <v>24.599999999999998</v>
       </c>
-      <c r="D6" s="89">
+      <c r="D6" s="76">
         <v>2.8237158649864519E-3</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="76">
         <v>5</v>
       </c>
-      <c r="G6" s="91">
+      <c r="G6" s="78">
         <v>39.700000000000003</v>
       </c>
-      <c r="H6" s="89">
+      <c r="H6" s="76">
         <v>3.649624853164684E-3</v>
       </c>
-      <c r="J6" s="92">
+      <c r="J6" s="79">
         <v>5</v>
       </c>
-      <c r="K6" s="93">
+      <c r="K6" s="80">
         <v>39.5</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="79">
         <v>4.1146636978582523E-3</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="89">
+      <c r="B7" s="76">
         <v>10</v>
       </c>
-      <c r="C7" s="90">
+      <c r="C7" s="77">
         <v>20.166666666666668</v>
       </c>
-      <c r="D7" s="89">
+      <c r="D7" s="76">
         <v>2.832086564190206E-3</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="76">
         <v>10</v>
       </c>
-      <c r="G7" s="91">
+      <c r="G7" s="78">
         <v>39.700000000000003</v>
       </c>
-      <c r="H7" s="89">
+      <c r="H7" s="76">
         <v>3.9872430544117977E-3</v>
       </c>
-      <c r="J7" s="92">
+      <c r="J7" s="79">
         <v>10</v>
       </c>
-      <c r="K7" s="93">
+      <c r="K7" s="80">
         <v>39.5</v>
       </c>
-      <c r="L7" s="92">
+      <c r="L7" s="79">
         <v>4.1741886699789687E-3</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B8" s="89">
+      <c r="B8" s="76">
         <v>20</v>
       </c>
-      <c r="C8" s="90">
+      <c r="C8" s="77">
         <v>20.2</v>
       </c>
-      <c r="D8" s="89">
+      <c r="D8" s="76">
         <v>2.667462813169002E-3</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="76">
         <v>20</v>
       </c>
-      <c r="G8" s="91">
+      <c r="G8" s="78">
         <v>39.700000000000003</v>
       </c>
-      <c r="H8" s="89">
+      <c r="H8" s="76">
         <v>3.9193473830871168E-3</v>
       </c>
-      <c r="J8" s="92">
+      <c r="J8" s="79">
         <v>20</v>
       </c>
-      <c r="K8" s="93">
+      <c r="K8" s="80">
         <v>39.5</v>
       </c>
-      <c r="L8" s="92">
+      <c r="L8" s="79">
         <v>4.4214730756448883E-3</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B9" s="89">
+      <c r="B9" s="76">
         <v>30</v>
       </c>
-      <c r="C9" s="90">
+      <c r="C9" s="77">
         <v>17.633333333333333</v>
       </c>
-      <c r="D9" s="89">
+      <c r="D9" s="76">
         <v>2.5825157175414721E-3</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="76">
         <v>30</v>
       </c>
-      <c r="G9" s="91">
+      <c r="G9" s="78">
         <v>36.5</v>
       </c>
-      <c r="H9" s="89">
+      <c r="H9" s="76">
         <v>3.9475597396674521E-3</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="79">
         <v>30</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="80">
         <v>39.5</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="79">
         <v>4.3868044297724392E-3</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B10" s="89">
+      <c r="B10" s="76">
         <v>40</v>
       </c>
-      <c r="C10" s="90">
+      <c r="C10" s="77">
         <v>15.266666666666666</v>
       </c>
-      <c r="D10" s="89">
+      <c r="D10" s="76">
         <v>2.5716648111675511E-3</v>
       </c>
-      <c r="F10" s="89">
+      <c r="F10" s="76">
         <v>40</v>
       </c>
-      <c r="G10" s="91">
+      <c r="G10" s="78">
         <v>34.799999999999997</v>
       </c>
-      <c r="H10" s="89">
+      <c r="H10" s="76">
         <v>3.9342286261162384E-3</v>
       </c>
-      <c r="J10" s="92">
+      <c r="J10" s="79">
         <v>40</v>
       </c>
-      <c r="K10" s="93">
+      <c r="K10" s="80">
         <v>39.5</v>
       </c>
-      <c r="L10" s="94">
+      <c r="L10" s="79">
         <v>4.3555538194055997E-3</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B11" s="89">
+      <c r="B11" s="76">
         <v>60</v>
       </c>
-      <c r="C11" s="90">
+      <c r="C11" s="77">
         <v>13.166666666666666</v>
       </c>
-      <c r="D11" s="89">
+      <c r="D11" s="76">
         <v>2.5879411707254727E-3</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="76">
         <v>60</v>
       </c>
-      <c r="G11" s="91">
+      <c r="G11" s="78">
         <v>29.633333333333336</v>
       </c>
-      <c r="H11" s="89">
+      <c r="H11" s="76">
         <v>3.8444761290949239E-3</v>
       </c>
-      <c r="J11" s="92">
+      <c r="J11" s="79">
         <v>60</v>
       </c>
-      <c r="K11" s="93">
+      <c r="K11" s="80">
         <v>32.275000000000006</v>
       </c>
-      <c r="L11" s="92">
+      <c r="L11" s="79">
         <v>4.0267713562129144E-3</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B12" s="89">
+      <c r="B12" s="76">
         <v>90</v>
       </c>
-      <c r="C12" s="90">
+      <c r="C12" s="77">
         <v>5.8999999999999995</v>
       </c>
-      <c r="D12" s="89">
+      <c r="D12" s="76">
         <v>2.7266157542214843E-3</v>
       </c>
-      <c r="F12" s="89">
+      <c r="F12" s="76">
         <v>90</v>
       </c>
-      <c r="G12" s="91">
+      <c r="G12" s="78">
         <v>23.400000000000002</v>
       </c>
-      <c r="H12" s="89">
+      <c r="H12" s="76">
         <v>3.2202777397982718E-3</v>
       </c>
-      <c r="J12" s="92">
+      <c r="J12" s="79">
         <v>90</v>
       </c>
-      <c r="K12" s="93">
+      <c r="K12" s="80">
         <v>30.099999999999998</v>
       </c>
-      <c r="L12" s="92">
+      <c r="L12" s="79">
         <v>3.8745870000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="89">
+      <c r="B13" s="76">
         <v>120</v>
       </c>
-      <c r="C13" s="90">
+      <c r="C13" s="77">
         <v>3.9666666666666663</v>
       </c>
-      <c r="D13" s="89"/>
-      <c r="F13" s="89">
+      <c r="D13" s="76"/>
+      <c r="F13" s="76">
         <v>120</v>
       </c>
-      <c r="G13" s="91">
+      <c r="G13" s="78">
         <v>15.633333333333333</v>
       </c>
-      <c r="H13" s="89">
+      <c r="H13" s="76">
         <v>3.1787730229110855E-3</v>
       </c>
-      <c r="J13" s="92">
+      <c r="J13" s="79">
         <v>120</v>
       </c>
-      <c r="K13" s="93">
+      <c r="K13" s="80">
         <v>24.433333333333334</v>
       </c>
-      <c r="L13" s="95">
+      <c r="L13" s="81">
         <f>AVERAGE(L12,L14)</f>
         <v>3.4375669428413158E-3</v>
       </c>
-      <c r="M13" s="95"/>
+      <c r="M13" s="81"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="F14" s="89">
+      <c r="F14" s="76">
         <v>150</v>
       </c>
-      <c r="G14" s="91">
+      <c r="G14" s="78">
         <v>11.799999999999999</v>
       </c>
-      <c r="H14" s="89"/>
-      <c r="J14" s="92">
+      <c r="H14" s="76"/>
+      <c r="J14" s="79">
         <v>137</v>
       </c>
-      <c r="L14" s="92">
+      <c r="L14" s="79">
         <v>3.0005468856826312E-3</v>
       </c>
-      <c r="M14" s="95">
+      <c r="M14" s="81">
         <v>137</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="J15" s="92">
+      <c r="J15" s="79">
         <v>150</v>
       </c>
-      <c r="K15" s="93">
+      <c r="K15" s="80">
         <v>15.933333333333332</v>
       </c>
     </row>

--- a/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
+++ b/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariajosetorresconstante/Documents/GitHub/SingleSolitaryWaveAnalysis/Pastas_Mortero_2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Desktop\InvestigacionUSFQ\SSWCompleteAnalysis\SingleSolitaryWaveAnalysis\Pastas_Mortero_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E4AD6C-9771-0740-8B91-78E146C420AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58131F07-FDD8-48AA-AEF8-6A6CFD11347B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="520" windowWidth="28800" windowHeight="15700" activeTab="3" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
   </bookViews>
   <sheets>
     <sheet name="CPT" sheetId="1" r:id="rId1"/>
@@ -450,6 +450,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1114,7 +1115,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1833,7 +1834,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2493,7 +2494,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3364,7 +3365,7 @@
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4037,7 +4038,7 @@
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4636,7 +4637,7 @@
 <file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5241,7 +5242,7 @@
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5901,7 +5902,7 @@
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6477,7 +6478,7 @@
 <file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7128,7 +7129,7 @@
 <file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7781,7 +7782,7 @@
 <file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8438,7 +8439,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9165,7 +9166,7 @@
 <file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9822,7 +9823,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10073,7 +10074,7 @@
                   <c:v>2.6050313482695042E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.8451076518468061E-3</c:v>
+                  <c:v>2.84510765184681E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10500,7 +10501,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11114,7 +11115,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11697,7 +11698,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11815,7 +11816,7 @@
                   <c:v>2.6050313482695042E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.8451076518468061E-3</c:v>
+                  <c:v>2.84510765184681E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12312,7 +12313,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12985,7 +12986,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13587,7 +13588,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -23265,20 +23266,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08DEF6F-9C93-4516-A42E-FF4987CDC52A}">
   <dimension ref="A1:X17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="6.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="2" max="7" width="6.796875" customWidth="1"/>
+    <col min="8" max="8" width="8.796875" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="6.83203125" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" customWidth="1"/>
+    <col min="10" max="15" width="6.796875" customWidth="1"/>
+    <col min="16" max="16" width="8.796875" customWidth="1"/>
     <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="6.83203125" customWidth="1"/>
-    <col min="24" max="24" width="8.83203125" customWidth="1"/>
+    <col min="18" max="23" width="6.796875" customWidth="1"/>
+    <col min="24" max="24" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B1" s="14" t="s">
         <v>9</v>
       </c>
@@ -23323,7 +23324,7 @@
       </c>
       <c r="P1" s="91"/>
     </row>
-    <row r="2" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
@@ -23369,7 +23370,7 @@
       </c>
       <c r="P2" s="93"/>
     </row>
-    <row r="3" spans="1:24" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="19" t="s">
         <v>10</v>
       </c>
@@ -23413,14 +23414,14 @@
       </c>
       <c r="P3" s="95"/>
     </row>
-    <row r="4" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="5"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="60">
         <v>45853</v>
       </c>
@@ -23458,7 +23459,7 @@
       <c r="W5" s="88"/>
       <c r="X5" s="89"/>
     </row>
-    <row r="6" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A6" s="28" t="s">
         <v>0</v>
       </c>
@@ -23532,7 +23533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="29" t="s">
         <v>1</v>
       </c>
@@ -23606,7 +23607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>0</v>
       </c>
@@ -23668,7 +23669,7 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -23721,7 +23722,7 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -23774,7 +23775,7 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>20</v>
       </c>
@@ -23827,7 +23828,7 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>30</v>
       </c>
@@ -23880,7 +23881,7 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>40</v>
       </c>
@@ -23936,7 +23937,7 @@
         <v>0.57128800898499266</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>60</v>
       </c>
@@ -24004,7 +24005,7 @@
         <v>0.85569067243829822</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>90</v>
       </c>
@@ -24069,7 +24070,7 @@
         <v>0.98382149867974411</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="3">
         <v>120</v>
       </c>
@@ -24133,7 +24134,7 @@
         <v>1.4930826881193389</v>
       </c>
     </row>
-    <row r="17" spans="9:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="I17" s="58">
         <v>150</v>
       </c>
@@ -24197,16 +24198,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF7CE1B-CDE6-724F-B93E-F8F0CB386150}">
   <dimension ref="B3:M30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B3" s="96">
         <v>0.3</v>
       </c>
@@ -24225,7 +24226,7 @@
       <c r="K3" s="97"/>
       <c r="L3" s="97"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B4" s="76"/>
       <c r="C4" s="76" t="s">
         <v>30</v>
@@ -24248,7 +24249,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B5" s="76">
         <v>0</v>
       </c>
@@ -24277,7 +24278,7 @@
         <v>3.541735841195178E-3</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B6" s="76">
         <v>5</v>
       </c>
@@ -24306,7 +24307,7 @@
         <v>4.1146636978582523E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B7" s="76">
         <v>10</v>
       </c>
@@ -24335,7 +24336,7 @@
         <v>4.1741886699789687E-3</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B8" s="76">
         <v>20</v>
       </c>
@@ -24364,7 +24365,7 @@
         <v>4.2539893357297128E-3</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B9" s="76">
         <v>30</v>
       </c>
@@ -24393,7 +24394,7 @@
         <v>4.2481298462847166E-3</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B10" s="76">
         <v>40</v>
       </c>
@@ -24422,7 +24423,7 @@
         <v>4.3018418328450991E-3</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B11" s="76">
         <v>60</v>
       </c>
@@ -24451,7 +24452,7 @@
         <v>3.9953037277208458E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B12" s="76">
         <v>90</v>
       </c>
@@ -24459,7 +24460,7 @@
         <v>5.8999999999999995</v>
       </c>
       <c r="D12" s="76">
-        <v>2.8451076518468061E-3</v>
+        <v>2.84510765184681E-3</v>
       </c>
       <c r="F12" s="76">
         <v>90</v>
@@ -24480,7 +24481,7 @@
         <v>3.4961620344202199E-3</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B13" s="76">
         <v>120</v>
       </c>
@@ -24509,7 +24510,7 @@
       </c>
       <c r="M13" s="81"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.45">
       <c r="F14" s="76">
         <v>150</v>
       </c>
@@ -24527,7 +24528,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
       <c r="J15" s="79">
         <v>150</v>
       </c>
@@ -24535,7 +24536,7 @@
         <v>15.933333333333332</v>
       </c>
     </row>
-    <row r="30" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="7:11" x14ac:dyDescent="0.45">
       <c r="G30">
         <v>0.5</v>
       </c>
@@ -24557,18 +24558,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE09722F-421D-0343-B16D-AF9646FD865B}">
   <dimension ref="B3:P15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1640625" customWidth="1"/>
+    <col min="9" max="9" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1328125" customWidth="1"/>
     <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1640625" customWidth="1"/>
+    <col min="14" max="14" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B3" s="96">
         <v>0.3</v>
       </c>
@@ -24590,7 +24591,7 @@
       <c r="N3" s="97"/>
       <c r="O3" s="97"/>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B4" s="76"/>
       <c r="C4" s="76" t="s">
         <v>30</v>
@@ -24622,7 +24623,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B5" s="76">
         <v>0</v>
       </c>
@@ -24660,7 +24661,7 @@
         <v>1.7012338793565899E-4</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B6" s="76">
         <v>5</v>
       </c>
@@ -24698,7 +24699,7 @@
         <v>1.749871409192086E-4</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B7" s="76">
         <v>10</v>
       </c>
@@ -24736,7 +24737,7 @@
         <v>1.1972018400394134E-4</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B8" s="76">
         <v>20</v>
       </c>
@@ -24774,7 +24775,7 @@
         <v>2.9016143340506438E-4</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B9" s="76">
         <v>30</v>
       </c>
@@ -24812,7 +24813,7 @@
         <v>4.3089275756920002E-4</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B10" s="76">
         <v>40</v>
       </c>
@@ -24850,7 +24851,7 @@
         <v>9.4850825756940651E-5</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B11" s="76">
         <v>60</v>
       </c>
@@ -24888,7 +24889,7 @@
         <v>3.0165324565052166E-4</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B12" s="76">
         <v>90</v>
       </c>
@@ -24924,7 +24925,7 @@
         <v>1.0331871738549517E-4</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B13" s="76">
         <v>120</v>
       </c>
@@ -24959,7 +24960,7 @@
       </c>
       <c r="P13" s="81"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.45">
       <c r="G14" s="76">
         <v>150</v>
       </c>
@@ -24977,7 +24978,7 @@
       <c r="O14" s="79"/>
       <c r="P14" s="81"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.45">
       <c r="L15" s="79">
         <v>150</v>
       </c>
@@ -24999,16 +25000,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506EE3AE-A1E5-BE4C-927B-DFA2FF39FD12}">
   <dimension ref="B3:M15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B3" s="96">
         <v>0.3</v>
       </c>
@@ -25027,7 +25028,7 @@
       <c r="K3" s="97"/>
       <c r="L3" s="97"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B4" s="76"/>
       <c r="C4" s="76" t="s">
         <v>30</v>
@@ -25050,7 +25051,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B5" s="76">
         <v>0</v>
       </c>
@@ -25079,7 +25080,7 @@
         <v>5.4363040944904739E-4</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B6" s="76">
         <v>5</v>
       </c>
@@ -25108,7 +25109,7 @@
         <v>6.8360710170223271E-4</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B7" s="76">
         <v>10</v>
       </c>
@@ -25137,7 +25138,7 @@
         <v>6.1943174113565647E-4</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B8" s="76">
         <v>20</v>
       </c>
@@ -25166,7 +25167,7 @@
         <v>6.7579444911043392E-4</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B9" s="76">
         <v>30</v>
       </c>
@@ -25195,7 +25196,7 @@
         <v>8.1381797821459634E-4</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B10" s="76">
         <v>40</v>
       </c>
@@ -25224,7 +25225,7 @@
         <v>7.7638235121924026E-4</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B11" s="76">
         <v>60</v>
       </c>
@@ -25253,7 +25254,7 @@
         <v>1.1762382511823057E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B12" s="76">
         <v>90</v>
       </c>
@@ -25282,7 +25283,7 @@
         <v>1.4697552686566695E-3</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B13" s="76">
         <v>120</v>
       </c>
@@ -25311,7 +25312,7 @@
       </c>
       <c r="M13" s="81"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.45">
       <c r="F14" s="76">
         <v>150</v>
       </c>
@@ -25327,7 +25328,7 @@
       </c>
       <c r="M14" s="81"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
       <c r="J15" s="79">
         <v>150</v>
       </c>
@@ -25349,9 +25350,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B63FB4-7123-F348-A6F1-6184B2E6168B}">
   <dimension ref="F3:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F3" s="96">
         <v>0.3</v>
       </c>
@@ -25367,7 +25368,7 @@
       </c>
       <c r="M3" s="97"/>
     </row>
-    <row r="4" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F4" s="76" t="s">
         <v>33</v>
       </c>
@@ -25389,7 +25390,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F5" s="76">
         <v>0</v>
       </c>
@@ -25409,7 +25410,7 @@
         <v>0.25554833400260607</v>
       </c>
     </row>
-    <row r="6" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F6" s="76">
         <v>5</v>
       </c>
@@ -25429,7 +25430,7 @@
         <v>0.20614531143966999</v>
       </c>
     </row>
-    <row r="7" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F7" s="76">
         <v>10</v>
       </c>
@@ -25449,7 +25450,7 @@
         <v>0.18409018132730282</v>
       </c>
     </row>
-    <row r="8" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F8" s="76">
         <v>20</v>
       </c>
@@ -25469,7 +25470,7 @@
         <v>0.1637309979276084</v>
       </c>
     </row>
-    <row r="9" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F9" s="76">
         <v>30</v>
       </c>
@@ -25489,7 +25490,7 @@
         <v>0.15351844904509085</v>
       </c>
     </row>
-    <row r="10" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F10" s="76">
         <v>40</v>
       </c>
@@ -25509,7 +25510,7 @@
         <v>0.18153388410121452</v>
       </c>
     </row>
-    <row r="11" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F11" s="76">
         <v>60</v>
       </c>
@@ -25529,7 +25530,7 @@
         <v>0.21458461131905143</v>
       </c>
     </row>
-    <row r="12" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F12" s="76">
         <v>90</v>
       </c>
@@ -25549,7 +25550,7 @@
         <v>0.18376979080188016</v>
       </c>
     </row>
-    <row r="13" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F13" s="76"/>
       <c r="G13" s="77"/>
       <c r="I13" s="76">
@@ -25565,7 +25566,7 @@
         <v>0.26641803575973444</v>
       </c>
     </row>
-    <row r="14" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="6:13" x14ac:dyDescent="0.45">
       <c r="I14" s="76"/>
       <c r="J14" s="78"/>
       <c r="L14" s="79"/>
@@ -25584,9 +25585,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5FF0E8-47F8-A449-925B-D33FA655E5FF}">
   <dimension ref="F3:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F3" s="96">
         <v>0.3</v>
       </c>
@@ -25602,7 +25603,7 @@
       </c>
       <c r="M3" s="97"/>
     </row>
-    <row r="4" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F4" s="76" t="s">
         <v>33</v>
       </c>
@@ -25624,7 +25625,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F5" s="76">
         <v>0</v>
       </c>
@@ -25644,7 +25645,7 @@
         <v>0.25554833400260607</v>
       </c>
     </row>
-    <row r="6" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F6" s="76">
         <v>5</v>
       </c>
@@ -25664,7 +25665,7 @@
         <v>0.20614531143966999</v>
       </c>
     </row>
-    <row r="7" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F7" s="76">
         <v>10</v>
       </c>
@@ -25684,7 +25685,7 @@
         <v>0.18409018132730282</v>
       </c>
     </row>
-    <row r="8" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F8" s="76">
         <v>20</v>
       </c>
@@ -25704,7 +25705,7 @@
         <v>0.1637309979276084</v>
       </c>
     </row>
-    <row r="9" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F9" s="76">
         <v>30</v>
       </c>
@@ -25724,7 +25725,7 @@
         <v>0.15351844904509085</v>
       </c>
     </row>
-    <row r="10" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F10" s="76">
         <v>40</v>
       </c>
@@ -25744,7 +25745,7 @@
         <v>0.18153388410121452</v>
       </c>
     </row>
-    <row r="11" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F11" s="76">
         <v>60</v>
       </c>
@@ -25764,7 +25765,7 @@
         <v>0.21458461131905143</v>
       </c>
     </row>
-    <row r="12" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F12" s="76">
         <v>90</v>
       </c>
@@ -25784,7 +25785,7 @@
         <v>0.18376979080188016</v>
       </c>
     </row>
-    <row r="13" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F13" s="76"/>
       <c r="G13" s="77"/>
       <c r="I13" s="76">
@@ -25800,7 +25801,7 @@
         <v>0.26641803575973444</v>
       </c>
     </row>
-    <row r="14" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="6:13" x14ac:dyDescent="0.45">
       <c r="I14" s="76"/>
       <c r="J14" s="78"/>
       <c r="L14" s="79"/>
@@ -25819,9 +25820,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7261E463-EB42-D147-BCFC-764A9DB56D35}">
   <dimension ref="F3:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F3" s="96">
         <v>0.3</v>
       </c>
@@ -25837,7 +25838,7 @@
       </c>
       <c r="M3" s="97"/>
     </row>
-    <row r="4" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F4" s="76" t="s">
         <v>33</v>
       </c>
@@ -25859,7 +25860,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F5" s="76">
         <v>0</v>
       </c>
@@ -25879,7 +25880,7 @@
         <v>0.36270460835165697</v>
       </c>
     </row>
-    <row r="6" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F6" s="76">
         <v>5</v>
       </c>
@@ -25899,7 +25900,7 @@
         <v>0.2905795879816</v>
       </c>
     </row>
-    <row r="7" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F7" s="76">
         <v>10</v>
       </c>
@@ -25919,7 +25920,7 @@
         <v>0.28747113629057258</v>
       </c>
     </row>
-    <row r="8" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F8" s="76">
         <v>20</v>
       </c>
@@ -25939,7 +25940,7 @@
         <v>0.24650243192800581</v>
       </c>
     </row>
-    <row r="9" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F9" s="76">
         <v>30</v>
       </c>
@@ -25959,7 +25960,7 @@
         <v>0.20798326005793896</v>
       </c>
     </row>
-    <row r="10" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F10" s="76">
         <v>40</v>
       </c>
@@ -25979,7 +25980,7 @@
         <v>0.24636845871801794</v>
       </c>
     </row>
-    <row r="11" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F11" s="76">
         <v>60</v>
       </c>
@@ -25999,7 +26000,7 @@
         <v>0.1863477774860024</v>
       </c>
     </row>
-    <row r="12" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F12" s="76">
         <v>90</v>
       </c>
@@ -26019,7 +26020,7 @@
         <v>0.17735448803325574</v>
       </c>
     </row>
-    <row r="13" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F13" s="76"/>
       <c r="G13" s="77"/>
       <c r="I13" s="76">
@@ -26035,7 +26036,7 @@
         <v>0.25240615317302034</v>
       </c>
     </row>
-    <row r="14" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="6:13" x14ac:dyDescent="0.45">
       <c r="I14" s="76"/>
       <c r="J14" s="78"/>
       <c r="L14" s="79"/>
@@ -26054,9 +26055,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60FD8A01-CBE9-9145-B1C1-FA8B852BDF18}">
   <dimension ref="F3:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F3" s="96">
         <v>0.3</v>
       </c>
@@ -26072,7 +26073,7 @@
       </c>
       <c r="M3" s="97"/>
     </row>
-    <row r="4" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F4" s="76" t="s">
         <v>33</v>
       </c>
@@ -26094,7 +26095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F5" s="76">
         <v>0</v>
       </c>
@@ -26114,7 +26115,7 @@
         <v>0.36270460835165697</v>
       </c>
     </row>
-    <row r="6" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F6" s="76">
         <v>5</v>
       </c>
@@ -26134,7 +26135,7 @@
         <v>0.2905795879816</v>
       </c>
     </row>
-    <row r="7" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F7" s="76">
         <v>10</v>
       </c>
@@ -26154,7 +26155,7 @@
         <v>0.28747113629057258</v>
       </c>
     </row>
-    <row r="8" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F8" s="76">
         <v>20</v>
       </c>
@@ -26174,7 +26175,7 @@
         <v>0.24650243192800581</v>
       </c>
     </row>
-    <row r="9" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F9" s="76">
         <v>30</v>
       </c>
@@ -26194,7 +26195,7 @@
         <v>0.20798326005793896</v>
       </c>
     </row>
-    <row r="10" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F10" s="76">
         <v>40</v>
       </c>
@@ -26214,7 +26215,7 @@
         <v>0.24636845871801794</v>
       </c>
     </row>
-    <row r="11" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F11" s="76">
         <v>60</v>
       </c>
@@ -26234,7 +26235,7 @@
         <v>0.1863477774860024</v>
       </c>
     </row>
-    <row r="12" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F12" s="76">
         <v>90</v>
       </c>
@@ -26254,7 +26255,7 @@
         <v>0.17735448803325574</v>
       </c>
     </row>
-    <row r="13" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="6:13" x14ac:dyDescent="0.45">
       <c r="F13" s="76"/>
       <c r="G13" s="77"/>
       <c r="I13" s="76">
@@ -26270,7 +26271,7 @@
         <v>0.25240615317302034</v>
       </c>
     </row>
-    <row r="14" spans="6:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="6:13" x14ac:dyDescent="0.45">
       <c r="I14" s="76"/>
       <c r="J14" s="78"/>
       <c r="L14" s="79"/>

--- a/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
+++ b/Pastas_Mortero_2025/Plantilla_RESULTADOS_CPT (072025).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariajosetorresconstante/Documents/GitHub/SingleSolitaryWaveAnalysis/Pastas_Mortero_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E4AD6C-9771-0740-8B91-78E146C420AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F264B7-5743-2C4E-BDB6-029C8A5003D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="520" windowWidth="28800" windowHeight="15700" activeTab="3" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15700" activeTab="1" xr2:uid="{6AC846BB-F0A6-40EE-9D25-7222205E4360}"/>
   </bookViews>
   <sheets>
     <sheet name="CPT" sheetId="1" r:id="rId1"/>
@@ -12412,10 +12412,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Penetración vs TOF (s)'!$C$5:$C$11</c:f>
+              <c:f>'Penetración vs TOF (s)'!$C$5:$C$12</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>25.166666666666668</c:v>
                 </c:pt>
@@ -12436,6 +12436,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>13.166666666666666</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8999999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12584,7 +12587,8 @@
         <c:axId val="1963225792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="75"/>
+          <c:max val="120"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
